--- a/T(K台)(P2-FU2)1150606K-版本16.11308(1131101更新).xlsx
+++ b/T(K台)(P2-FU2)1150606K-版本16.11308(1131101更新).xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\95078\Desktop\AOOOI\TSP_Excel_Batch_Unlock_V3\OUTPUT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\95078\Desktop\高量採集自動收件\TSP_Excel_Batch_Unlock_V3\OUTPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{43CD7183-1711-45AF-9CE4-4058C605F8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E94A0C58-0CAC-4016-8981-C8C76168FEB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13667"/>
   </bookViews>
@@ -2013,7 +2013,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DA73-4C89-B855-295204054052}"/>
+              <c16:uniqueId val="{00000001-834C-40D6-864A-A164696A2F17}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2025,11 +2025,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1161142463"/>
+        <c:axId val="376250992"/>
         <c:axId val="1"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1161142463"/>
+        <c:axId val="376250992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.8"/>
@@ -2250,7 +2250,7 @@
             <a:endParaRPr lang="zh-TW"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1161142463"/>
+        <c:crossAx val="376250992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2324,7 +2324,7 @@
         <xdr:cNvPr id="1917967" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14AE957B-E9E7-454C-84F0-AF44D2972ED2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04D1BF10-A6E3-4735-89BC-1C2D284E335F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2362,7 +2362,7 @@
         <xdr:cNvPr id="3" name="文字方塊 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85277BCF-124C-4F70-B76A-AA644470AA2A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DB5460A6-B320-465B-BE2F-A1C7C86937FA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2442,7 +2442,7 @@
         <xdr:cNvPr id="1917969" name="圖片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99FA87A4-D69F-4CF4-A9F7-A2DDE525555C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABF7A43B-A403-4FE9-9477-31A39C11E727}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2516,7 +2516,7 @@
         <xdr:cNvPr id="1917970" name="圖片 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDBE2E71-C80F-4013-B35A-A7013CC80F77}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BB3667A-B455-415C-864D-1DC836C1D88B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2590,7 +2590,7 @@
         <xdr:cNvPr id="6" name="文字方塊 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{458A192D-674A-42CC-B29A-A44770FC0CFF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{878053BF-2EAF-44CF-ABCC-3C029EBA94F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2670,7 +2670,7 @@
         <xdr:cNvPr id="1917972" name="圖片 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D1BF918-5874-4B38-A20E-BE5FAA3A93DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAE5555C-07A6-4E76-8D23-0D0396F1B5F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2744,7 +2744,7 @@
         <xdr:cNvPr id="1917973" name="圖片 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8FB05BCE-CA12-452E-921B-46089E1CCC48}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AAAA413-E427-4516-94B2-F2795609DE79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
